--- a/data/merged/2026-09-23/MERGED_IT_Wet-Dry-Floor-Washer_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_IT_Wet-Dry-Floor-Washer_2026-09-23.xlsx
@@ -918,50 +918,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Product 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1303,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR4"/>
+  <dimension ref="A1:BR3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -1948,56 +1904,52 @@
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>B0G66L48KD</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>Taglia: 20L - 1200W</t>
-        </is>
-      </c>
+          <t>B0G7GJZ7WQ</t>
+        </is>
+      </c>
+      <c r="D3" s="14"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Bosch | Fonte di alimentazione: ac_dc | Tensione: 240 Volt | Componenti inclusi: Dotazione: PAS20-220, 2 tubi di prolunga (plastica), 1 tubo di aspirazione (2,2 m), 1 tubo a gomito/impugnatura, 1 bocchetta per pavimenti, 1 bocchetta per fessure, 1 borsa in tessuto (Uni), 1 filtro plissettato piatto, 1 UniversalAdapter | È cordless?: No</t>
+          <t>Marchio: JONR | Caratteristica speciale: Duo-Clean | Tipo di filtro: Sistema di filtrazione multistadio | Superfici consigliate: Tutti i tipi di pavimento | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>JONR</t>
         </is>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/BoschDIY/page/C0E50987-D148-4E3F-80C4-79212A89392F?lp_asin=B0G66L48KD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>Bosch Aspiratore solidi-liquidi PAS20-220P (Tubi di prolunga, tubo di aspirazione 2,2 m, tubo a gomito/impugnatura, bocchette, borsa in tessuto (Uni), filtro plissettato piatto, UniversalAdapter)</t>
+          <t>JONR 20000 Pa H2 aspirapolvere a secco bagnato,Design Innovativo Protezione Odori,Serbatoio Acqua Extra Grande 1500ml con Posizione Piatta a 180° (Potenza Aspirazione e Acqua Inalterate),45 Min. (S)</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>Motore da 1.200 W con potenza di aspirazione di 220 mbar: rimuove senza sforzo lo sporco umido e secco
-Filtro pieghettato piatto: per aspirare liquidi e residui secchi senza cambiare il filtro
-Funzione di soffiaggio: rimuove lo sporco dalle zone difficilmente accessibili
-Movimento facile e stabile: con contenitore da 20 l e ruote antiribaltamento
-Dotazione: PAS20-220, 2 tubi di prolunga (plastica), 1 tubo di aspirazione (2,2 m), 1 tubo a gomito/impugnatura, 1 bocchetta per pavimenti, 1 bocchetta per fessure, 1 borsa in tessuto (Uni), 1 filtro plissettato piatto, 1 UniversalAdapter</t>
+          <t>20.000 Pa di potente aspirazione e doppie spazzole laterali assicurano una copertura completa da bordo a bordo, il rullo ad alta velocità da 500 RPM e lo spazzolamento pressorizzato sollevano facilmente lo sporco ostinato.
+Leader Leggero del Mercato, Guida Tu - 3.5kg / 7.7lb Il punto di riferimento del settore consente una facile operazione con una mano senza ingombro. Pulizia con trazione auto-drive, senza sforzo come una passeggiata, assemblaggio/smontaggio in 3 secondi per una manutenzione senza attrezzi e senza mani
+Prestazioni leader della batteria, pulisce tutta la casa in un unico passaggio - 45 minuti di pulizia potente puliscono grandi spazi dall'inizio alla fine senza ricarica. Il serbatoio dell'acqua pulita da 50,7 Fl oz / 1500 ml consente una pulizia dell'intera casa con acqua fresca. La base di ricarica salvaspazio inizia a caricare immediatamente al momento della connessione
+Trattenere rifiuti solidi e liquidi, prevenendo odori e crescita fungina - Il filtro monouso e biodegradabile trattiene le macchie liquide, eliminando le preoccupazioni per i residui che si attaccano alle pareti, il serbatoio dell'acqua sporca da 650 ml montato sul fondo isola i rifiuti, previene il riflusso e contiene gli odori, il motore impermeabile con classificazione IPX6 e la pulizia diretta dell'acqua del rullo fermano gli odori e i funghi — un must per i proprietari di animali domestici
+Totalmente piatto a 180° - Posizione completamente piatta a 180°, mantenendo la piena potenza di aspirazione per scivolare sotto i mobili e affrontare aree difficili da raggiungere e basse.</t>
         </is>
       </c>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0G66L48KD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/416etd8+eUL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>B0H6MY3KH1</t>
+          <t>B0G7GJZ7WQ</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
@@ -2011,13 +1963,11 @@
         </is>
       </c>
       <c r="O3" s="15">
-        <v>112800</v>
-      </c>
-      <c r="P3" s="15">
-        <v>95511</v>
-      </c>
+        <v>908657</v>
+      </c>
+      <c r="P3" s="15"/>
       <c r="Q3" s="16">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="R3" s="17" t="inlineStr">
         <is>
@@ -2026,69 +1976,61 @@
       </c>
       <c r="S3" s="18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T3" s="15">
-        <v>20</v>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" s="15"/>
       <c r="U3" s="16"/>
-      <c r="V3" s="15">
-        <v>3300</v>
-      </c>
+      <c r="V3" s="15"/>
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
       <c r="Y3" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="20">
-        <v>135.24</v>
+        <v>298.41</v>
       </c>
       <c r="AA3" s="4"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="19">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AE3" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="21">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AG3" s="22">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="20">
-        <v>10.91</v>
+        <v>10.56</v>
       </c>
       <c r="AI3" s="16">
-        <v>0.78</v>
+        <v>0.81</v>
       </c>
       <c r="AJ3"/>
       <c r="AK3" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AL3" s="19">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="AM3" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN3" s="13" t="inlineStr">
-        <is>
-          <t>15天</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN3" s="13"/>
       <c r="AO3" s="13"/>
-      <c r="AP3" s="20">
-        <v>122.12</v>
-      </c>
-      <c r="AQ3" s="19"/>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="19">
+        <v>9</v>
+      </c>
       <c r="AR3" s="19">
         <v>1</v>
       </c>
@@ -2099,7 +2041,7 @@
       </c>
       <c r="AT3" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU3" s="13"/>
@@ -2115,7 +2057,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD3" s="13"/>
+      <c r="BD3" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE3" s="13"/>
       <c r="BF3" s="13"/>
       <c r="BG3" s="13"/>
@@ -2123,245 +2069,37 @@
       <c r="BI3"/>
       <c r="BJ3" s="23" t="inlineStr">
         <is>
-          <t>6 Chilogrammi</t>
+          <t>3,5 Chilogrammi</t>
         </is>
       </c>
       <c r="BK3" s="23"/>
       <c r="BL3" s="23" t="inlineStr">
         <is>
-          <t>37,6L x 36,5l x 49,2H cm</t>
+          <t>27L x 21l x 110H cm</t>
         </is>
       </c>
       <c r="BM3" s="23"/>
       <c r="BN3" s="23" t="inlineStr">
         <is>
-          <t>9.89 kg</t>
+          <t>6.78 kg</t>
         </is>
       </c>
       <c r="BO3" s="23" t="inlineStr">
         <is>
-          <t>9.89 kg</t>
+          <t>6.78 kg</t>
         </is>
       </c>
       <c r="BP3" s="23" t="inlineStr">
         <is>
-          <t>51.5 x 39.8 x 38.5 cm</t>
+          <t>61 x 33.8 x 32.3 cm</t>
         </is>
       </c>
       <c r="BQ3" s="23" t="inlineStr">
         <is>
-          <t>51.50 x 39.80 x 38.50 cm</t>
+          <t>61.00 x 33.80 x 32.30 cm</t>
         </is>
       </c>
       <c r="BR3" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>B0G7GJZ7WQ</t>
-        </is>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>Marchio: JONR | Caratteristica speciale: Duo-Clean | Tipo di filtro: Sistema di filtrazione multistadio | Superfici consigliate: Tutti i tipi di pavimento | Fonte di alimentazione: A batteria</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>JONR</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>JONR 20000 Pa H2 aspirapolvere a secco bagnato,Design Innovativo Protezione Odori,Serbatoio Acqua Extra Grande 1500ml con Posizione Piatta a 180° (Potenza Aspirazione e Acqua Inalterate),45 Min. (S)</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>20.000 Pa di potente aspirazione e doppie spazzole laterali assicurano una copertura completa da bordo a bordo, il rullo ad alta velocità da 500 RPM e lo spazzolamento pressorizzato sollevano facilmente lo sporco ostinato.
-Leader Leggero del Mercato, Guida Tu - 3.5kg / 7.7lb Il punto di riferimento del settore consente una facile operazione con una mano senza ingombro. Pulizia con trazione auto-drive, senza sforzo come una passeggiata, assemblaggio/smontaggio in 3 secondi per una manutenzione senza attrezzi e senza mani
-Prestazioni leader della batteria, pulisce tutta la casa in un unico passaggio - 45 minuti di pulizia potente puliscono grandi spazi dall'inizio alla fine senza ricarica. Il serbatoio dell'acqua pulita da 50,7 Fl oz / 1500 ml consente una pulizia dell'intera casa con acqua fresca. La base di ricarica salvaspazio inizia a caricare immediatamente al momento della connessione
-Trattenere rifiuti solidi e liquidi, prevenendo odori e crescita fungina - Il filtro monouso e biodegradabile trattiene le macchie liquide, eliminando le preoccupazioni per i residui che si attaccano alle pareti, il serbatoio dell'acqua sporca da 650 ml montato sul fondo isola i rifiuti, previene il riflusso e contiene gli odori, il motore impermeabile con classificazione IPX6 e la pulizia diretta dell'acqua del rullo fermano gli odori e i funghi — un must per i proprietari di animali domestici
-Totalmente piatto a 180° - Posizione completamente piatta a 180°, mantenendo la piena potenza di aspirazione per scivolare sotto i mobili e affrontare aree difficili da raggiungere e basse.</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1</t>
-        </is>
-      </c>
-      <c r="K4" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>B0G7GJZ7WQ</t>
-        </is>
-      </c>
-      <c r="M4" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspiratori solidi-liquidi per uso domestico</t>
-        </is>
-      </c>
-      <c r="N4" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O4" s="15">
-        <v>908657</v>
-      </c>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="16">
-        <v>0</v>
-      </c>
-      <c r="R4" s="17" t="inlineStr">
-        <is>
-          <t>Aspiratori solidi-liquidi per uso domestico</t>
-        </is>
-      </c>
-      <c r="S4" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T4" s="15"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="20">
-        <v>298.41</v>
-      </c>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="19">
-        <v>48</v>
-      </c>
-      <c r="AE4" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="21">
-        <v>3.5</v>
-      </c>
-      <c r="AG4" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="20">
-        <v>10.56</v>
-      </c>
-      <c r="AI4" s="16">
-        <v>0.81</v>
-      </c>
-      <c r="AJ4"/>
-      <c r="AK4" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AL4" s="19">
-        <v>188</v>
-      </c>
-      <c r="AM4" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN4" s="13"/>
-      <c r="AO4" s="13"/>
-      <c r="AP4" s="20"/>
-      <c r="AQ4" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR4" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT4" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="14"/>
-      <c r="AW4" s="13"/>
-      <c r="AX4" s="13"/>
-      <c r="AY4" s="13"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="13"/>
-      <c r="BC4" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD4" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE4" s="13"/>
-      <c r="BF4" s="13"/>
-      <c r="BG4" s="13"/>
-      <c r="BH4" s="14"/>
-      <c r="BI4"/>
-      <c r="BJ4" s="23" t="inlineStr">
-        <is>
-          <t>3,5 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK4" s="23"/>
-      <c r="BL4" s="23" t="inlineStr">
-        <is>
-          <t>27L x 21l x 110H cm</t>
-        </is>
-      </c>
-      <c r="BM4" s="23"/>
-      <c r="BN4" s="23" t="inlineStr">
-        <is>
-          <t>6.78 kg</t>
-        </is>
-      </c>
-      <c r="BO4" s="23" t="inlineStr">
-        <is>
-          <t>6.78 kg</t>
-        </is>
-      </c>
-      <c r="BP4" s="23" t="inlineStr">
-        <is>
-          <t>61 x 33.8 x 32.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ4" s="23" t="inlineStr">
-        <is>
-          <t>61.00 x 33.80 x 32.30 cm</t>
-        </is>
-      </c>
-      <c r="BR4" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
@@ -2378,28 +2116,21 @@
     <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.it/dp/B0H3NV8G7Q"/>
     <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.it/b?node=218944968031"/>
     <hyperlink ref="N2" r:id="rId7"/>
-    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.it/dp/B0G66L48KD"/>
-    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.it/stores/BoschDIY/page/C0E50987-D148-4E3F-80C4-79212A89392F?lp_asin=B0G66L48KD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.it/dp/B0G66L48KD?psc=1"/>
-    <hyperlink ref="K3" r:id="rId11" tooltip="https://m.media-amazon.com/images/I/416etd8+eUL._AC_US600_.jpg"/>
-    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.it/dp/B0H6MY3KH1"/>
+    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
+    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1"/>
+    <hyperlink ref="K3" r:id="rId11" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
     <hyperlink ref="M3" r:id="rId13" tooltip="https://www.amazon.it/b?node=218944968031"/>
     <hyperlink ref="N3" r:id="rId14"/>
-    <hyperlink ref="C4" r:id="rId15" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="G4" r:id="rId16" tooltip="https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J4" r:id="rId17" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1"/>
-    <hyperlink ref="K4" r:id="rId18" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg"/>
-    <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.it/b?node=218944968031"/>
-    <hyperlink ref="N4" r:id="rId21"/>
   </hyperlinks>
-  <drawing r:id="rId22"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -2463,46 +2194,25 @@
         <v>169.99019607843138</v>
       </c>
       <c r="G2" s="22">
-        <v>0.8360655737704918</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>JONR</t>
         </is>
       </c>
       <c r="B3" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C3" s="15">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
-      <c r="F3" s="20">
-        <v>165.0</v>
-      </c>
+      <c r="F3" s="20"/>
       <c r="G3" s="22">
-        <v>0.16393442622950818</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>JONR</t>
-        </is>
-      </c>
-      <c r="B4" s="15">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -2567,15 +2277,15 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C2" s="15">
-        <v>20639</v>
+        <v>17339</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>169.172131147541</v>
+        <v>169.99019607843138</v>
       </c>
       <c r="G2" s="22">
         <v>1.0</v>
